--- a/src/test/resources/testdata/Modules/14_QueryList/QueryList/01_QueryListTest.xlsx
+++ b/src/test/resources/testdata/Modules/14_QueryList/QueryList/01_QueryListTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\14_QueryList\QueryList\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F128D71A-7688-46DC-A91A-DE37BE7CCF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2122E26E-6A9B-49C7-8F96-01991FBD2223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -320,7 +320,18 @@
 verify_pagetitle</t>
   </si>
   <si>
+    <t>QueryListTest_19</t>
+  </si>
+  <si>
+    <t>Relaunch app</t>
+  </si>
+  <si>
+    <t>terminateapp
+relaunchapp</t>
+  </si>
+  <si>
     <t>navigatebacktodashboardpage
+open_querylist_menu
 clickon_fabbtn
 clickon_querytype
 select_querytype_dropvalue
@@ -328,16 +339,6 @@
 enter_detailsdesc
 clickon_submitbtn
 verify_snackbar</t>
-  </si>
-  <si>
-    <t>QueryListTest_19</t>
-  </si>
-  <si>
-    <t>Relaunch app</t>
-  </si>
-  <si>
-    <t>terminateapp
-relaunchapp</t>
   </si>
 </sst>
 </file>
@@ -1766,13 +1767,13 @@
       <c r="I17" s="1"/>
       <c r="J17" s="5"/>
       <c r="K17" s="10" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="116" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
@@ -1786,7 +1787,7 @@
         <v>44</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -1840,13 +1841,13 @@
         <v>10</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="E20" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>

--- a/src/test/resources/testdata/Modules/14_QueryList/QueryList/01_QueryListTest.xlsx
+++ b/src/test/resources/testdata/Modules/14_QueryList/QueryList/01_QueryListTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\14_QueryList\QueryList\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2122E26E-6A9B-49C7-8F96-01991FBD2223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B359DE-F711-40BF-83C3-2F251C81B531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -235,17 +235,6 @@
 verify_pagetitle</t>
   </si>
   <si>
-    <t>clickon_querytype
-select_querytype_dropvalue
-enter_briefdesc
-enter_detailsdesc
-clickon_imageicon
-clickon_cameracaptureicon
-clickon_cameracapturedonebtn
-clickon_submitbtn
-verify_snackbar</t>
-  </si>
-  <si>
     <t>verify_emailvalue</t>
   </si>
   <si>
@@ -337,6 +326,19 @@
 select_querytype_dropvalue
 enter_briefdesc
 enter_detailsdesc
+clickon_submitbtn
+verify_snackbar</t>
+  </si>
+  <si>
+    <t>clickon_querytype
+select_querytype_dropvalue
+enter_briefdesc
+enter_detailsdesc
+clickon_imageicon
+clickon_cameracaptureicon
+clickon_cameracaptureicon
+clickon_cameracapturedonebtn
+clickon_cameracapturedonebtn
 clickon_submitbtn
 verify_snackbar</t>
   </si>
@@ -1363,7 +1365,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="5"/>
       <c r="K3" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>5</v>
@@ -1383,7 +1385,7 @@
         <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -1391,7 +1393,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="5"/>
       <c r="K4" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>5</v>
@@ -1419,7 +1421,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="5"/>
       <c r="K5" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>5</v>
@@ -1439,19 +1441,19 @@
         <v>16</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="5"/>
       <c r="K6" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>5</v>
@@ -1471,19 +1473,19 @@
         <v>17</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="5"/>
       <c r="K7" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>5</v>
@@ -1511,7 +1513,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="5"/>
       <c r="K8" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>5</v>
@@ -1539,7 +1541,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="5"/>
       <c r="K9" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>5</v>
@@ -1559,7 +1561,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -1567,7 +1569,7 @@
       <c r="I10" s="1"/>
       <c r="J10" s="5"/>
       <c r="K10" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>5</v>
@@ -1595,13 +1597,13 @@
       <c r="I11" s="1"/>
       <c r="J11" s="5"/>
       <c r="K11" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1615,7 +1617,7 @@
         <v>22</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -1627,7 +1629,7 @@
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>5</v>
@@ -1655,7 +1657,7 @@
       <c r="I13" s="1"/>
       <c r="J13" s="5"/>
       <c r="K13" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>5</v>
@@ -1683,7 +1685,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="5"/>
       <c r="K14" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>5</v>
@@ -1787,7 +1789,7 @@
         <v>44</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -1799,7 +1801,7 @@
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>5</v>
@@ -1816,10 +1818,10 @@
         <v>45</v>
       </c>
       <c r="D19" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -1827,7 +1829,7 @@
       <c r="I19" s="1"/>
       <c r="J19" s="5"/>
       <c r="K19" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>5</v>
@@ -1841,13 +1843,13 @@
         <v>10</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="E20" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
